--- a/model_comparison.xlsx
+++ b/model_comparison.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,7 +805,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EfficientNetB4_vs2</t>
+          <t>EfficientNetB4_vs1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -859,160 +859,241 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>ResNet152_RAFDB</t>
+          <t>MobileNetV2_vs1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.8423 ± 0.0522</t>
+          <t>0.8068 ± 0.0512</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.7689 ± 0.0379</t>
+          <t>0.7408 ± 0.0341</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.7965 ± 0.0517</t>
+          <t>0.7384 ± 0.0645</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.7765 ± 0.0516</t>
+          <t>0.7332 ± 0.0561</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>ResNet152_vs1</t>
+          <t>MobileNetV3_RAFDB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0813</t>
+          <t>0.8183 ± 0.0422</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.7412 ± 0.0574</t>
+          <t>0.7465 ± 0.0302</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.7430 ± 0.0878</t>
+          <t>0.7512 ± 0.0531</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.7349 ± 0.0817</t>
+          <t>0.7442 ± 0.0457</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>ResNet50_RAFDB</t>
+          <t>MobileNetV3_vs1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.8229 ± 0.0561</t>
+          <t>0.8203 ± 0.0383</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.7554 ± 0.0366</t>
+          <t>0.7474 ± 0.0209</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.7542 ± 0.0558</t>
+          <t>0.7510 ± 0.0485</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.7504 ± 0.0558</t>
+          <t>0.7443 ± 0.0396</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>vit_base_patch16_224_RAFDB</t>
+          <t>ResNet152_RAFDB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.8423 ± 0.0242</t>
+          <t>0.8423 ± 0.0522</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.7574 ± 0.0154</t>
+          <t>0.7689 ± 0.0379</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.7649 ± 0.0306</t>
+          <t>0.7965 ± 0.0517</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.7590 ± 0.0253</t>
+          <t>0.7765 ± 0.0516</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>vit_base_patch16_224_vs1</t>
+          <t>ResNet152_vs1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.8426 ± 0.0323</t>
+          <t>0.8100 ± 0.0813</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.7670 ± 0.0211</t>
+          <t>0.7412 ± 0.0574</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.7730 ± 0.0416</t>
+          <t>0.7430 ± 0.0878</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.7669 ± 0.0344</t>
+          <t>0.7349 ± 0.0817</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>ResNet50_RAFDB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.8229 ± 0.0561</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.7554 ± 0.0366</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.7542 ± 0.0558</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.7504 ± 0.0558</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>vit_base_patch16_224_RAFDB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.8423 ± 0.0242</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.7574 ± 0.0154</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.7649 ± 0.0306</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.7590 ± 0.0253</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>vit_base_patch16_224_vs1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.8426 ± 0.0323</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.7670 ± 0.0211</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.7730 ± 0.0416</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.7669 ± 0.0344</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
           <t>vit_base_patch16_224_vs2</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.8469 ± 0.0359</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>0.7657 ± 0.0144</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.7867 ± 0.0424</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>0.7699 ± 0.0328</t>
         </is>
@@ -1029,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,22 +1440,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.6851 ± 0.0250</t>
+          <t>0.6854 ± 0.0219</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.6645 ± 0.0215</t>
+          <t>0.6666 ± 0.0190</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.6914 ± 0.0359</t>
+          <t>0.6949 ± 0.0339</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.6736 ± 0.0296</t>
+          <t>0.6766 ± 0.0275</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1494,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.6968 ± 0.0161</t>
+          <t>0.6935 ± 0.0187</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.6747 ± 0.0126</t>
+          <t>0.6706 ± 0.0147</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.7090 ± 0.0264</t>
+          <t>0.7033 ± 0.0289</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.6872 ± 0.0207</t>
+          <t>0.6823 ± 0.0230</t>
         </is>
       </c>
     </row>
@@ -1462,160 +1543,241 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>ResNet152_FER2013</t>
+          <t>MobileNetV2_vs1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.6741 ± 0.0351</t>
+          <t>0.6553 ± 0.0262</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.6545 ± 0.0299</t>
+          <t>0.6402 ± 0.0231</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.6826 ± 0.0442</t>
+          <t>0.6586 ± 0.0464</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.6622 ± 0.0431</t>
+          <t>0.6440 ± 0.0387</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>ResNet152_vs1</t>
+          <t>MobileNetV3_FER2013</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.6647 ± 0.0468</t>
+          <t>0.8183 ± 0.0422</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.6487 ± 0.0444</t>
+          <t>0.7465 ± 0.0302</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.6626 ± 0.0656</t>
+          <t>0.7512 ± 0.0531</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.6504 ± 0.0598</t>
+          <t>0.7442 ± 0.0457</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>ResNet50_FER2013</t>
+          <t>MobileNetV3_vs1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.6768 ± 0.0263</t>
+          <t>0.8203 ± 0.0383</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.6618 ± 0.0226</t>
+          <t>0.7474 ± 0.0209</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.6847 ± 0.0362</t>
+          <t>0.7510 ± 0.0485</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.6684 ± 0.0353</t>
+          <t>0.7443 ± 0.0396</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>ResNet50_vs1</t>
+          <t>ResNet152_FER2013</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.6535 ± 0.0421</t>
+          <t>0.6741 ± 0.0351</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.6411 ± 0.0398</t>
+          <t>0.6545 ± 0.0299</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.6449 ± 0.0616</t>
+          <t>0.6826 ± 0.0442</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.6382 ± 0.0557</t>
+          <t>0.6622 ± 0.0431</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>vit_base_patch16_224_FER2013</t>
+          <t>ResNet152_vs1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.7067 ± 0.0162</t>
+          <t>0.5113 ± 0.1103</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.6834 ± 0.0149</t>
+          <t>0.5016 ± 0.1033</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.7081 ± 0.0204</t>
+          <t>0.4803 ± 0.1018</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.6919 ± 0.0179</t>
+          <t>0.4745 ± 0.1182</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>ResNet50_FER2013</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.6768 ± 0.0263</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.6618 ± 0.0226</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.6847 ± 0.0362</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.6684 ± 0.0353</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ResNet50_vs1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.6535 ± 0.0421</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.6411 ± 0.0398</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.6449 ± 0.0616</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.6382 ± 0.0557</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>vit_base_patch16_224_FER2013</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.7067 ± 0.0162</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.6834 ± 0.0149</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.7081 ± 0.0204</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.6919 ± 0.0179</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
           <t>vit_base_patch16_224_vs1</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.7067 ± 0.0154</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>0.6840 ± 0.0127</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.7075 ± 0.0247</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>0.6925 ± 0.0196</t>
         </is>

--- a/model_comparison.xlsx
+++ b/model_comparison.xlsx
@@ -459,22 +459,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.8303 ± 0.0484</t>
+          <t>0.8385 ± 0.0381</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.7768 ± 0.0340</t>
+          <t>0.7770 ± 0.0254</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.7707 ± 0.0569</t>
+          <t>0.7809 ± 0.0450</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.7682 ± 0.0516</t>
+          <t>0.7739 ± 0.0396</t>
         </is>
       </c>
     </row>
@@ -513,22 +513,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0633</t>
+          <t>0.8116 ± 0.0622</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7469 ± 0.0537</t>
+          <t>0.7476 ± 0.0524</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.7289 ± 0.0638</t>
+          <t>0.7287 ± 0.0619</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.7293 ± 0.0726</t>
+          <t>0.7299 ± 0.0706</t>
         </is>
       </c>
     </row>
@@ -621,22 +621,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.7909 ± 0.0911</t>
+          <t>0.7936 ± 0.0932</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7410 ± 0.0766</t>
+          <t>0.7429 ± 0.0782</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.7225 ± 0.0660</t>
+          <t>0.7228 ± 0.0659</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.7180 ± 0.0957</t>
+          <t>0.7191 ± 0.0970</t>
         </is>
       </c>
     </row>
@@ -729,22 +729,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.8010 ± 0.0277</t>
+          <t>0.8107 ± 0.0221</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.7321 ± 0.0218</t>
+          <t>0.7339 ± 0.0171</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.7218 ± 0.0353</t>
+          <t>0.7338 ± 0.0285</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.7194 ± 0.0298</t>
+          <t>0.7288 ± 0.0238</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.8377 ± 0.0301</t>
+          <t>0.8388 ± 0.0261</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.7609 ± 0.0223</t>
+          <t>0.7487 ± 0.0152</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.7826 ± 0.0416</t>
+          <t>0.7806 ± 0.0387</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.7670 ± 0.0351</t>
+          <t>0.7582 ± 0.0290</t>
         </is>
       </c>
     </row>
@@ -837,22 +837,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.8078 ± 0.0506</t>
+          <t>0.8102 ± 0.0482</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.7368 ± 0.0324</t>
+          <t>0.7365 ± 0.0302</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.7327 ± 0.0596</t>
+          <t>0.7366 ± 0.0573</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.7295 ± 0.0513</t>
+          <t>0.7315 ± 0.0486</t>
         </is>
       </c>
     </row>
@@ -945,22 +945,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.8423 ± 0.0522</t>
+          <t>0.8306 ± 0.0637</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.7689 ± 0.0379</t>
+          <t>0.7633 ± 0.0473</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.7965 ± 0.0517</t>
+          <t>0.7804 ± 0.0606</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.7765 ± 0.0516</t>
+          <t>0.7658 ± 0.0632</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.8229 ± 0.0561</t>
+          <t>0.8266 ± 0.0522</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.7554 ± 0.0366</t>
+          <t>0.7556 ± 0.0333</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.7542 ± 0.0558</t>
+          <t>0.7598 ± 0.0525</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.7504 ± 0.0558</t>
+          <t>0.7534 ± 0.0515</t>
         </is>
       </c>
     </row>
@@ -1143,22 +1143,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.6677 ± 0.0318</t>
+          <t>0.6669 ± 0.0319</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.6539 ± 0.0283</t>
+          <t>0.6532 ± 0.0284</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.6701 ± 0.0495</t>
+          <t>0.6677 ± 0.0489</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.6561 ± 0.0448</t>
+          <t>0.6547 ± 0.0447</t>
         </is>
       </c>
     </row>
@@ -1197,22 +1197,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6704 ± 0.0414</t>
+          <t>0.6638 ± 0.0444</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6581 ± 0.0380</t>
+          <t>0.6519 ± 0.0408</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6723 ± 0.0516</t>
+          <t>0.6657 ± 0.0561</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6604 ± 0.0509</t>
+          <t>0.6530 ± 0.0550</t>
         </is>
       </c>
     </row>
@@ -1251,22 +1251,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.6786 ± 0.0223</t>
+          <t>0.6788 ± 0.0224</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.6638 ± 0.0191</t>
+          <t>0.6637 ± 0.0192</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.6847 ± 0.0314</t>
+          <t>0.6863 ± 0.0323</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.6708 ± 0.0278</t>
+          <t>0.6713 ± 0.0282</t>
         </is>
       </c>
     </row>
@@ -1305,22 +1305,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.6525 ± 0.0516</t>
+          <t>0.6559 ± 0.0498</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.6431 ± 0.0419</t>
+          <t>0.6454 ± 0.0403</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.6524 ± 0.0578</t>
+          <t>0.6541 ± 0.0547</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.6410 ± 0.0632</t>
+          <t>0.6437 ± 0.0604</t>
         </is>
       </c>
     </row>
@@ -1359,22 +1359,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.6821 ± 0.0211</t>
+          <t>0.6864 ± 0.0177</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.6630 ± 0.0203</t>
+          <t>0.6665 ± 0.0168</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.6901 ± 0.0323</t>
+          <t>0.6960 ± 0.0269</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.6726 ± 0.0267</t>
+          <t>0.6775 ± 0.0222</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1413,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.6799 ± 0.0230</t>
+          <t>0.6921 ± 0.0181</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.6627 ± 0.0172</t>
+          <t>0.6723 ± 0.0131</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.6868 ± 0.0349</t>
+          <t>0.7081 ± 0.0285</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.6701 ± 0.0288</t>
+          <t>0.6851 ± 0.0224</t>
         </is>
       </c>
     </row>
@@ -1467,22 +1467,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.6862 ± 0.0206</t>
+          <t>0.6924 ± 0.0163</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.6630 ± 0.0160</t>
+          <t>0.6686 ± 0.0120</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.6911 ± 0.0198</t>
+          <t>0.7062 ± 0.0207</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.6728 ± 0.0190</t>
+          <t>0.6827 ± 0.0159</t>
         </is>
       </c>
     </row>
@@ -1521,22 +1521,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.6647 ± 0.0227</t>
+          <t>0.6643 ± 0.0230</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.6476 ± 0.0175</t>
+          <t>0.6472 ± 0.0177</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.6737 ± 0.0391</t>
+          <t>0.6732 ± 0.0396</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.6546 ± 0.0320</t>
+          <t>0.6543 ± 0.0325</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1629,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.6741 ± 0.0351</t>
+          <t>0.6713 ± 0.0381</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.6545 ± 0.0299</t>
+          <t>0.6539 ± 0.0333</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.6826 ± 0.0442</t>
+          <t>0.6822 ± 0.0494</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.6622 ± 0.0431</t>
+          <t>0.6609 ± 0.0477</t>
         </is>
       </c>
     </row>
@@ -1683,22 +1683,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.6768 ± 0.0263</t>
+          <t>0.6783 ± 0.0256</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.6618 ± 0.0226</t>
+          <t>0.6646 ± 0.0226</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.6847 ± 0.0362</t>
+          <t>0.6896 ± 0.0365</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.6684 ± 0.0353</t>
+          <t>0.6724 ± 0.0352</t>
         </is>
       </c>
     </row>

--- a/model_comparison.xlsx
+++ b/model_comparison.xlsx
@@ -8,20 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\CTU\Final_LuanVan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C4D3F4-B79B-48E5-85E0-06DD4CF85312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2D100C-DEE5-4F92-9DF3-165CD5E5CB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RAFDB" sheetId="1" r:id="rId1"/>
     <sheet name="FER2013" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="234">
   <si>
     <t>Accuracy</t>
   </si>
@@ -720,6 +733,9 @@
   </si>
   <si>
     <t>0.6925 ± 0.0196</t>
+  </si>
+  <si>
+    <t>Loại</t>
   </si>
 </sst>
 </file>
@@ -748,7 +764,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -771,13 +787,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1082,13 +1110,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1101,8 +1130,11 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1118,412 +1150,513 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A2)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A3)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A4)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A5)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A6)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A7)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A8)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A9)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A10)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A11)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A12)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" t="s">
+        <v>113</v>
+      </c>
+      <c r="F13" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A13)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A14)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B15" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C15" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="F15" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A15)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D16" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="F16" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A16)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C17" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D17" t="s">
         <v>32</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E17" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="F17" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A17)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B18" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C18" t="s">
         <v>41</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D18" t="s">
         <v>42</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E18" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="F18" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A18)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B19" t="s">
         <v>50</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C19" t="s">
         <v>51</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D19" t="s">
         <v>52</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E19" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="F19" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A19)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B20" t="s">
         <v>65</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C20" t="s">
         <v>66</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D20" t="s">
         <v>67</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E20" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="F20" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A20)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B21" t="s">
         <v>75</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C21" t="s">
         <v>76</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D21" t="s">
         <v>77</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E21" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="F21" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A21)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B22" t="s">
         <v>85</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C22" t="s">
         <v>86</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D22" t="s">
         <v>87</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E22" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" t="s">
-        <v>92</v>
-      </c>
-      <c r="E19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="F22" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A22)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B23" t="s">
         <v>95</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C23" t="s">
         <v>96</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D23" t="s">
         <v>97</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E23" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="F23" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A23)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B24" t="s">
         <v>105</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C24" t="s">
         <v>106</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D24" t="s">
         <v>107</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E24" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="F24" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A24)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>115</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>116</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>117</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B25" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" t="s">
-        <v>121</v>
-      </c>
-      <c r="D25" t="s">
-        <v>122</v>
-      </c>
-      <c r="E25" t="s">
-        <v>123</v>
+      <c r="F25" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A25)),"vs1","Khác")</f>
+        <v>vs1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F25">
+    <sortCondition ref="F2:F25"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1536,8 +1669,11 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>124</v>
       </c>
@@ -1553,382 +1689,474 @@
       <c r="E2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A2)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A3)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A4)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A5)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F6" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A6)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A7)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F8" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A8)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" t="s">
+        <v>192</v>
+      </c>
+      <c r="F9" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A9)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A10)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" t="s">
+        <v>208</v>
+      </c>
+      <c r="D11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" t="s">
+        <v>210</v>
+      </c>
+      <c r="F11" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A11)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E12" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A12)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" t="s">
+        <v>225</v>
+      </c>
+      <c r="C13" t="s">
+        <v>226</v>
+      </c>
+      <c r="D13" t="s">
+        <v>227</v>
+      </c>
+      <c r="E13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F13" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A13)),"vs1","Khác")</f>
+        <v>Khác</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B14" t="s">
         <v>129</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C14" t="s">
         <v>130</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D14" t="s">
         <v>131</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E14" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="F14" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A14)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B15" t="s">
         <v>138</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C15" t="s">
         <v>139</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D15" t="s">
         <v>140</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E15" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="F15" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A15)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B16" t="s">
         <v>147</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C16" t="s">
         <v>148</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D16" t="s">
         <v>149</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E16" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" t="s">
-        <v>154</v>
-      </c>
-      <c r="E8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="F16" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A16)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B17" t="s">
         <v>156</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C17" t="s">
         <v>157</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D17" t="s">
         <v>158</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E17" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B10" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="F17" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A17)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B18" t="s">
         <v>165</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C18" t="s">
         <v>166</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D18" t="s">
         <v>167</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E18" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" t="s">
-        <v>172</v>
-      </c>
-      <c r="E12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="F18" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A18)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B19" t="s">
         <v>175</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C19" t="s">
         <v>176</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D19" t="s">
         <v>177</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E19" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C14" t="s">
-        <v>181</v>
-      </c>
-      <c r="D14" t="s">
-        <v>182</v>
-      </c>
-      <c r="E14" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="F19" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A19)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B20" t="s">
         <v>184</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C20" t="s">
         <v>185</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D20" t="s">
         <v>186</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E20" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B16" t="s">
-        <v>189</v>
-      </c>
-      <c r="C16" t="s">
-        <v>190</v>
-      </c>
-      <c r="D16" t="s">
-        <v>191</v>
-      </c>
-      <c r="E16" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="F20" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A20)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B21" t="s">
         <v>193</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C21" t="s">
         <v>194</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D21" t="s">
         <v>195</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E21" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B18" t="s">
-        <v>198</v>
-      </c>
-      <c r="C18" t="s">
-        <v>199</v>
-      </c>
-      <c r="D18" t="s">
-        <v>200</v>
-      </c>
-      <c r="E18" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="F21" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A21)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B22" t="s">
         <v>202</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C22" t="s">
         <v>203</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D22" t="s">
         <v>204</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E22" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B20" t="s">
-        <v>207</v>
-      </c>
-      <c r="C20" t="s">
-        <v>208</v>
-      </c>
-      <c r="D20" t="s">
-        <v>209</v>
-      </c>
-      <c r="E20" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="F22" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A22)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B23" t="s">
         <v>211</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C23" t="s">
         <v>212</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D23" t="s">
         <v>213</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E23" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B22" t="s">
-        <v>216</v>
-      </c>
-      <c r="C22" t="s">
-        <v>217</v>
-      </c>
-      <c r="D22" t="s">
-        <v>218</v>
-      </c>
-      <c r="E22" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="F23" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A23)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>220</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>221</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>222</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B24" t="s">
-        <v>225</v>
-      </c>
-      <c r="C24" t="s">
-        <v>226</v>
-      </c>
-      <c r="D24" t="s">
-        <v>227</v>
-      </c>
-      <c r="E24" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A24)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>114</v>
       </c>
@@ -1944,8 +2172,15 @@
       <c r="E25" t="s">
         <v>232</v>
       </c>
+      <c r="F25" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A25)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F25">
+    <sortCondition ref="F2:F25"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/model_comparison.xlsx
+++ b/model_comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\CTU\Final_LuanVan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2D100C-DEE5-4F92-9DF3-165CD5E5CB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1612FC-3D70-4063-A459-48EF9E96BD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RAFDB" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="238">
   <si>
     <t>Accuracy</t>
   </si>
@@ -213,6 +213,21 @@
     <t>0.7727 ± 0.0320</t>
   </si>
   <si>
+    <t>EfficientNetB3_vs1</t>
+  </si>
+  <si>
+    <t>0.8387 ± 0.0422</t>
+  </si>
+  <si>
+    <t>0.7630 ± 0.0248</t>
+  </si>
+  <si>
+    <t>0.7734 ± 0.0522</t>
+  </si>
+  <si>
+    <t>0.7636 ± 0.0445</t>
+  </si>
+  <si>
     <t>EfficientNetB4_RAFDB</t>
   </si>
   <si>
@@ -556,9 +571,6 @@
   </si>
   <si>
     <t>0.6851 ± 0.0224</t>
-  </si>
-  <si>
-    <t>EfficientNetB3_vs1</t>
   </si>
   <si>
     <t>0.6854 ± 0.0219</t>
@@ -1110,11 +1122,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -1131,7 +1143,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1262,19 +1274,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F8" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A8)),"vs1","Khác")</f>
@@ -1283,19 +1295,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F9" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A9)),"vs1","Khác")</f>
@@ -1304,19 +1316,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F10" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A10)),"vs1","Khác")</f>
@@ -1325,19 +1337,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F11" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A11)),"vs1","Khác")</f>
@@ -1346,19 +1358,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F12" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A12)),"vs1","Khác")</f>
@@ -1367,19 +1379,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F13" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A13)),"vs1","Khác")</f>
@@ -1388,19 +1400,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F14" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A14)),"vs1","Khác")</f>
@@ -1514,19 +1526,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F20" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A20)),"vs1","Khác")</f>
@@ -1535,19 +1547,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F21" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A21)),"vs1","Khác")</f>
@@ -1556,19 +1568,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F22" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A22)),"vs1","Khác")</f>
@@ -1577,19 +1589,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F23" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A23)),"vs1","Khác")</f>
@@ -1598,19 +1610,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F24" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A24)),"vs1","Khác")</f>
@@ -1619,28 +1631,49 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E25" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F25" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A25)),"vs1","Khác")</f>
         <v>vs1</v>
       </c>
     </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" t="str">
+        <f>IF(ISNUMBER(SEARCH("vs1",A26)),"vs1","Khác")</f>
+        <v>vs1</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F25">
-    <sortCondition ref="F2:F25"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F26">
+    <sortCondition ref="F2:F26"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1652,8 +1685,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -1670,24 +1703,24 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F2" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A2)),"vs1","Khác")</f>
@@ -1696,19 +1729,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F3" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A3)),"vs1","Khác")</f>
@@ -1717,19 +1750,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F4" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A4)),"vs1","Khác")</f>
@@ -1738,19 +1771,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F5" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A5)),"vs1","Khác")</f>
@@ -1759,19 +1792,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F6" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A6)),"vs1","Khác")</f>
@@ -1780,19 +1813,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E7" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F7" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A7)),"vs1","Khác")</f>
@@ -1801,19 +1834,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F8" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A8)),"vs1","Khác")</f>
@@ -1822,19 +1855,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F9" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A9)),"vs1","Khác")</f>
@@ -1843,19 +1876,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E10" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F10" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A10)),"vs1","Khác")</f>
@@ -1864,19 +1897,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B11" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D11" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E11" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F11" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A11)),"vs1","Khác")</f>
@@ -1885,19 +1918,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C12" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E12" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F12" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A12)),"vs1","Khác")</f>
@@ -1906,19 +1939,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B13" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D13" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E13" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F13" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A13)),"vs1","Khác")</f>
@@ -1930,16 +1963,16 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F14" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A14)),"vs1","Khác")</f>
@@ -1951,16 +1984,16 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F15" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A15)),"vs1","Khác")</f>
@@ -1972,16 +2005,16 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F16" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A16)),"vs1","Khác")</f>
@@ -1993,16 +2026,16 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C17" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E17" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F17" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A17)),"vs1","Khác")</f>
@@ -2014,16 +2047,16 @@
         <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C18" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D18" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E18" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F18" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A18)),"vs1","Khác")</f>
@@ -2032,19 +2065,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D19" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E19" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F19" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A19)),"vs1","Khác")</f>
@@ -2053,19 +2086,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C20" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E20" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F20" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A20)),"vs1","Khác")</f>
@@ -2074,19 +2107,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D21" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E21" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F21" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A21)),"vs1","Khác")</f>
@@ -2095,19 +2128,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C22" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D22" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E22" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F22" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A22)),"vs1","Khác")</f>
@@ -2116,19 +2149,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B23" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C23" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D23" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E23" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F23" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A23)),"vs1","Khác")</f>
@@ -2137,19 +2170,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B24" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C24" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D24" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E24" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F24" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A24)),"vs1","Khác")</f>
@@ -2158,19 +2191,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C25" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D25" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E25" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F25" t="str">
         <f>IF(ISNUMBER(SEARCH("vs1",A25)),"vs1","Khác")</f>
